--- a/reports/LeetcodeDaily Report 2 year_2026-10-22.xlsx
+++ b/reports/LeetcodeDaily Report 2 year_2026-10-22.xlsx
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>89</v>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
